--- a/tame_output/ON/bt/strategyON_20231020.xlsx
+++ b/tame_output/ON/bt/strategyON_20231020.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,16 +911,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>100.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.1%</t>
+          <t>-157.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.8%</t>
+          <t>130.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>15.7%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1755"/>
+  <dimension ref="A1:G1756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41875,7 +41875,7 @@
         <v>45217</v>
       </c>
       <c r="B1755" t="n">
-        <v>2.85500603633627</v>
+        <v>2.855532085778605</v>
       </c>
       <c r="C1755" t="n">
         <v>2.95420083304114</v>
@@ -41891,6 +41891,29 @@
       </c>
       <c r="G1755" t="n">
         <v>4.252781427532267</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="2" t="n">
+        <v>45218</v>
+      </c>
+      <c r="B1756" t="n">
+        <v>2.892346310831684</v>
+      </c>
+      <c r="C1756" t="n">
+        <v>2.969006534107256</v>
+      </c>
+      <c r="D1756" t="n">
+        <v>1.564540301344227</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>3.5944662303312</v>
+      </c>
+      <c r="F1756" t="n">
+        <v>2.164300990818542</v>
+      </c>
+      <c r="G1756" t="n">
+        <v>4.267587128598383</v>
       </c>
     </row>
   </sheetData>
